--- a/data/verben.xlsx
+++ b/data/verben.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jwt/Documents/Code/gelato/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2A844A-F013-CC4B-BCE7-5FB5DBC5364E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286C55AC-A8E0-AA48-9E30-EEE0219D9701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3920" yWindow="1680" windowWidth="28800" windowHeight="18000" xr2:uid="{0B0E448C-6A3E-9144-8554-BD4609B1F373}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{0B0E448C-6A3E-9144-8554-BD4609B1F373}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
